--- a/software/curves/3. Final Round/X018_LM/curve_0.0_2_Reverse.xlsx
+++ b/software/curves/3. Final Round/X018_LM/curve_0.0_2_Reverse.xlsx
@@ -1,21 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Walker Arce\Documents\GitHub\Perovskite-Curve-Tracer\software\curves\3. Final Round\X018_LM\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47657C09-8AD6-4C6B-8FBF-51F3A56E0661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Data" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>Time</t>
   </si>
@@ -76,15 +95,27 @@
   <si>
     <t>Power</t>
   </si>
+  <si>
+    <t>Jsc</t>
+  </si>
+  <si>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>Pmax</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -100,16 +131,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -132,29 +176,57 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -192,7 +264,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -226,6 +298,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -260,9 +333,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -435,16 +509,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -452,7 +526,7 @@
         <v>45215.64698599081</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -460,7 +534,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -468,15 +542,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.058</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>5.8000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -484,7 +558,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -492,15 +566,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0.004820512820512821</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>4.8205128205128208E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -508,15 +582,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0.7118290598290599</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>0.71182905982905986</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -524,15 +598,15 @@
         <v>1.165744930450813</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.8298111178432948</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>0.82981111784329475</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -540,15 +614,15 @@
         <v>8298111.178432948</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0.143070882386775</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>0.14307088238677501</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -562,11 +636,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E257"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:N257"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="6" max="6" width="10.453125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
@@ -579,297 +656,361 @@
       <c r="E1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="G1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.004820512820512821</v>
+        <v>4.8205128205128208E-3</v>
       </c>
       <c r="C2">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D2">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E2">
-        <v>0.006682634833464397</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>6.6826348334643971E-3</v>
+      </c>
+      <c r="F2" s="6">
+        <v>45215</v>
+      </c>
+      <c r="G2" s="4">
+        <f>MAX(E2:E257)/(C2*B234)</f>
+        <v>0.62399116796101706</v>
+      </c>
+      <c r="H2" s="8">
+        <f>MAX(B2:B257)</f>
+        <v>0.9608888888888889</v>
+      </c>
+      <c r="I2" s="9">
+        <f>MAX(D2:D257)</f>
+        <v>23.901573597313959</v>
+      </c>
+      <c r="J2" s="5">
+        <f>(L2/100)</f>
+        <v>0.14331053210601577</v>
+      </c>
+      <c r="K2">
+        <f>MAX(C2:C257)</f>
+        <v>1.3862912686442099</v>
+      </c>
+      <c r="L2">
+        <f>(H2*K2*G2)/0.058</f>
+        <v>14.331053210601578</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.006427350427350428</v>
+        <v>6.4273504273504277E-3</v>
       </c>
       <c r="C3">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D3">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E3">
-        <v>0.008910179777952529</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>8.9101797779525295E-3</v>
+      </c>
+      <c r="F3" s="6">
+        <v>45177</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.747</v>
+      </c>
+      <c r="H3" s="8">
+        <v>1.0960000000000001</v>
+      </c>
+      <c r="I3">
+        <v>22.6</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.006427350427350428</v>
+        <v>6.4273504273504277E-3</v>
       </c>
       <c r="C4">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D4">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E4">
-        <v>0.008910179777952529</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>8.9101797779525295E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5">
-        <v>0.009641025641025642</v>
+        <v>9.6410256410256415E-3</v>
       </c>
       <c r="C5">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D5">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E5">
-        <v>0.01336526966692879</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+        <v>1.3365269666928791E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>0.01285470085470086</v>
+        <v>1.2854700854700861E-2</v>
       </c>
       <c r="C6">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D6">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E6">
-        <v>0.01782035955590506</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>1.7820359555905059E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7">
-        <v>0.01606837606837607</v>
+        <v>1.6068376068376071E-2</v>
       </c>
       <c r="C7">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D7">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E7">
-        <v>0.02227544944488132</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>2.2275449444881319E-2</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8">
-        <v>0.02088888888888889</v>
+        <v>2.0888888888888891E-2</v>
       </c>
       <c r="C8">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D8">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E8">
-        <v>0.02895808427834572</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>2.895808427834572E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>0.02570940170940171</v>
+        <v>2.5709401709401711E-2</v>
       </c>
       <c r="C9">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D9">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E9">
-        <v>0.03564071911181012</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>3.5640719111810118E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>8</v>
       </c>
       <c r="B10">
-        <v>0.03213675213675213</v>
+        <v>3.2136752136752128E-2</v>
       </c>
       <c r="C10">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D10">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E10">
-        <v>0.04455089888976264</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>4.4550898889762637E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>9</v>
       </c>
       <c r="B11">
-        <v>0.04017094017094017</v>
+        <v>4.0170940170940167E-2</v>
       </c>
       <c r="C11">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D11">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E11">
-        <v>0.05568862361220331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>5.5688623612203308E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>10</v>
       </c>
       <c r="B12">
-        <v>0.0465982905982906</v>
+        <v>4.6598290598290598E-2</v>
       </c>
       <c r="C12">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D12">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E12">
-        <v>0.06459880339015583</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>6.4598803390155835E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>11</v>
       </c>
       <c r="B13">
-        <v>0.05302564102564103</v>
+        <v>5.3025641025641029E-2</v>
       </c>
       <c r="C13">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D13">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E13">
-        <v>0.07350898316810837</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>7.3508983168108374E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>12</v>
       </c>
       <c r="B14">
-        <v>0.06105982905982906</v>
+        <v>6.1059829059829061E-2</v>
       </c>
       <c r="C14">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D14">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E14">
-        <v>0.08464670789054902</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>8.4646707890549025E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>13</v>
       </c>
       <c r="B15">
-        <v>0.06748717948717949</v>
+        <v>6.7487179487179486E-2</v>
       </c>
       <c r="C15">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D15">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E15">
-        <v>0.09355688766850155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>9.3556887668501551E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16">
-        <v>0.07391452991452992</v>
+        <v>7.3914529914529917E-2</v>
       </c>
       <c r="C16">
         <v>1.378414613708731</v>
       </c>
       <c r="D16">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E16">
         <v>0.1018848681995992</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17">
-        <v>0.08194871794871794</v>
+        <v>8.1948717948717942E-2</v>
       </c>
       <c r="C17">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D17">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E17">
         <v>0.1136047921688947</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>16</v>
       </c>
       <c r="B18">
-        <v>0.0931965811965812</v>
+        <v>9.3196581196581196E-2</v>
       </c>
       <c r="C18">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D18">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E18">
         <v>0.1291976067803117</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -877,16 +1018,16 @@
         <v>0.1060512820512821</v>
       </c>
       <c r="C19">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D19">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E19">
-        <v>0.1470179663362167</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
+        <v>0.14701796633621669</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -894,50 +1035,50 @@
         <v>0.1172991452991453</v>
       </c>
       <c r="C20">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D20">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E20">
         <v>0.1626107809476337</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21">
-        <v>0.1285470085470085</v>
+        <v>0.12854700854700851</v>
       </c>
       <c r="C21">
         <v>1.378414613708731</v>
       </c>
       <c r="D21">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E21">
-        <v>0.1771910751297378</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
+        <v>0.17719107512973781</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>20</v>
       </c>
       <c r="B22">
-        <v>0.1381880341880342</v>
+        <v>0.13818803418803419</v>
       </c>
       <c r="C22">
         <v>1.378414613708731</v>
       </c>
       <c r="D22">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E22">
-        <v>0.1904804057644681</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+        <v>0.19048040576446809</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -948,13 +1089,13 @@
         <v>1.378414613708731</v>
       </c>
       <c r="D23">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E23">
-        <v>0.2015548479600767</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
+        <v>0.20155484796007669</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -965,64 +1106,64 @@
         <v>1.378414613708731</v>
       </c>
       <c r="D24">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E24">
-        <v>0.214844178594807</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
+        <v>0.21484417859480701</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25">
-        <v>0.1655042735042735</v>
+        <v>0.16550427350427349</v>
       </c>
       <c r="C25">
-        <v>1.38629126864421</v>
+        <v>1.3862912686442099</v>
       </c>
       <c r="D25">
-        <v>23.90157359731396</v>
+        <v>23.901573597313959</v>
       </c>
       <c r="E25">
-        <v>0.2294371292822776</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+        <v>0.22943712928227761</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26">
-        <v>0.1751452991452991</v>
+        <v>0.17514529914529911</v>
       </c>
       <c r="C26">
         <v>1.378414613708731</v>
       </c>
       <c r="D26">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E26">
-        <v>0.2414228398642677</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
+        <v>0.24142283986426771</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27">
-        <v>0.1847863247863248</v>
+        <v>0.18478632478632481</v>
       </c>
       <c r="C27">
         <v>1.378414613708731</v>
       </c>
       <c r="D27">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E27">
-        <v>0.254712170498998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
+        <v>0.25471217049899803</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1033,13 +1174,13 @@
         <v>1.378414613708731</v>
       </c>
       <c r="D28">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E28">
-        <v>0.2657866126946066</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
+        <v>0.26578661269460663</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1050,47 +1191,47 @@
         <v>1.378414613708731</v>
       </c>
       <c r="D29">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E29">
         <v>0.279075943329337</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>28</v>
       </c>
       <c r="B30">
-        <v>0.2121025641025641</v>
+        <v>0.21210256410256409</v>
       </c>
       <c r="C30">
         <v>1.378414613708731</v>
       </c>
       <c r="D30">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E30">
-        <v>0.2923652739640673</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+        <v>0.29236527396406731</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>29</v>
       </c>
       <c r="B31">
-        <v>0.2201367521367522</v>
+        <v>0.22013675213675221</v>
       </c>
       <c r="C31">
         <v>1.378414613708731</v>
       </c>
       <c r="D31">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E31">
-        <v>0.3034397161596759</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
+        <v>0.30343971615967591</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1101,13 +1242,13 @@
         <v>1.378414613708731</v>
       </c>
       <c r="D32">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E32">
-        <v>0.3145141583552845</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>0.31451415835528451</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1118,64 +1259,64 @@
         <v>1.378414613708731</v>
       </c>
       <c r="D33">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E33">
-        <v>0.3233737121117715</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
+        <v>0.32337371211177152</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>32</v>
       </c>
       <c r="B34">
-        <v>0.2538803418803419</v>
+        <v>0.25388034188034192</v>
       </c>
       <c r="C34">
         <v>1.378414613708731</v>
       </c>
       <c r="D34">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E34">
-        <v>0.3499523733812321</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
+        <v>0.34995237338123208</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>33</v>
       </c>
       <c r="B35">
-        <v>0.2715555555555556</v>
+        <v>0.27155555555555561</v>
       </c>
       <c r="C35">
         <v>1.378414613708731</v>
       </c>
       <c r="D35">
-        <v>23.76576920187468</v>
+        <v>23.765769201874679</v>
       </c>
       <c r="E35">
         <v>0.374316146211571</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36">
-        <v>0.2876239316239316</v>
+        <v>0.28762393162393157</v>
       </c>
       <c r="C36">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D36">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E36">
-        <v>0.3941995161422009</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>0.39419951614220089</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -1183,305 +1324,305 @@
         <v>0.3020854700854701</v>
       </c>
       <c r="C37">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D37">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E37">
-        <v>0.4140196035459988</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
+        <v>0.41401960354599882</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>36</v>
       </c>
       <c r="B38">
-        <v>0.314940170940171</v>
+        <v>0.31494017094017102</v>
       </c>
       <c r="C38">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D38">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E38">
-        <v>0.4316374590160412</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
+        <v>0.43163745901604123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>37</v>
       </c>
       <c r="B39">
-        <v>0.3261880341880342</v>
+        <v>0.32618803418803421</v>
       </c>
       <c r="C39">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D39">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E39">
-        <v>0.4470530825523285</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
+        <v>0.44705308255232851</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>38</v>
       </c>
       <c r="B40">
-        <v>0.3374358974358974</v>
+        <v>0.33743589743589741</v>
       </c>
       <c r="C40">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D40">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E40">
-        <v>0.4624687060886156</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
+        <v>0.46246870608861562</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="B41">
-        <v>0.3486837606837607</v>
+        <v>0.34868376068376072</v>
       </c>
       <c r="C41">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D41">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E41">
-        <v>0.4778843296249028</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
+        <v>0.47788432962490279</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="B42">
-        <v>0.3599316239316239</v>
+        <v>0.35993162393162392</v>
       </c>
       <c r="C42">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D42">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E42">
-        <v>0.49329995316119</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
+        <v>0.49329995316119002</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>41</v>
       </c>
       <c r="B43">
-        <v>0.3711794871794872</v>
+        <v>0.37117948717948718</v>
       </c>
       <c r="C43">
-        <v>1.370537958773253</v>
+        <v>1.3705379587732529</v>
       </c>
       <c r="D43">
-        <v>23.62996480643539</v>
+        <v>23.629964806435389</v>
       </c>
       <c r="E43">
-        <v>0.5087155766974771</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
+        <v>0.50871557669747713</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>42</v>
       </c>
       <c r="B44">
-        <v>0.3824273504273504</v>
+        <v>0.38242735042735038</v>
       </c>
       <c r="C44">
         <v>1.362661303837774</v>
       </c>
       <c r="D44">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E44">
-        <v>0.5211189519565588</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
+        <v>0.52111895195655877</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>43</v>
       </c>
       <c r="B45">
-        <v>0.3904615384615385</v>
+        <v>0.39046153846153853</v>
       </c>
       <c r="C45">
         <v>1.362661303837774</v>
       </c>
       <c r="D45">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E45">
-        <v>0.5320668290985033</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
+        <v>0.53206682909850334</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>44</v>
       </c>
       <c r="B46">
-        <v>0.4017094017094017</v>
+        <v>0.40170940170940173</v>
       </c>
       <c r="C46">
         <v>1.362661303837774</v>
       </c>
       <c r="D46">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E46">
-        <v>0.5473938570972257</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
+        <v>0.54739385709722566</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>45</v>
       </c>
       <c r="B47">
-        <v>0.4097435897435898</v>
+        <v>0.40974358974358982</v>
       </c>
       <c r="C47">
-        <v>1.354784648902296</v>
+        <v>1.3547846489022961</v>
       </c>
       <c r="D47">
-        <v>23.35835601555682</v>
+        <v>23.358356015556819</v>
       </c>
       <c r="E47">
-        <v>0.5551143253707356</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
+        <v>0.55511432537073557</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>46</v>
       </c>
       <c r="B48">
-        <v>0.4177777777777777</v>
+        <v>0.41777777777777769</v>
       </c>
       <c r="C48">
         <v>1.362661303837774</v>
       </c>
       <c r="D48">
-        <v>23.49416041099611</v>
+        <v>23.494160410996109</v>
       </c>
       <c r="E48">
-        <v>0.5692896113811146</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
+        <v>0.56928961138111456</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>47</v>
       </c>
       <c r="B49">
-        <v>0.4258119658119658</v>
+        <v>0.42581196581196579</v>
       </c>
       <c r="C49">
-        <v>1.354784648902296</v>
+        <v>1.3547846489022961</v>
       </c>
       <c r="D49">
-        <v>23.35835601555682</v>
+        <v>23.358356015556819</v>
       </c>
       <c r="E49">
-        <v>0.5768835146009604</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
+        <v>0.57688351460096043</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>48</v>
       </c>
       <c r="B50">
-        <v>0.4386666666666666</v>
+        <v>0.43866666666666659</v>
       </c>
       <c r="C50">
-        <v>1.354784648902296</v>
+        <v>1.3547846489022961</v>
       </c>
       <c r="D50">
-        <v>23.35835601555682</v>
+        <v>23.358356015556819</v>
       </c>
       <c r="E50">
-        <v>0.5942988659851404</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+        <v>0.59429886598514037</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>49</v>
       </c>
       <c r="B51">
-        <v>0.4515213675213675</v>
+        <v>0.45152136752136751</v>
       </c>
       <c r="C51">
-        <v>1.354784648902296</v>
+        <v>1.3547846489022961</v>
       </c>
       <c r="D51">
-        <v>23.35835601555682</v>
+        <v>23.358356015556819</v>
       </c>
       <c r="E51">
         <v>0.6117142173693203</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>50</v>
       </c>
       <c r="B52">
-        <v>0.4611623931623932</v>
+        <v>0.46116239316239321</v>
       </c>
       <c r="C52">
-        <v>1.354784648902296</v>
+        <v>1.3547846489022961</v>
       </c>
       <c r="D52">
-        <v>23.35835601555682</v>
+        <v>23.358356015556819</v>
       </c>
       <c r="E52">
         <v>0.6247757309074552</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>51</v>
       </c>
       <c r="B53">
-        <v>0.4724102564102564</v>
+        <v>0.47241025641025641</v>
       </c>
       <c r="C53">
         <v>1.346907993966818</v>
       </c>
       <c r="D53">
-        <v>23.22255162011754</v>
+        <v>23.222551620117539</v>
       </c>
       <c r="E53">
-        <v>0.6362931507908884</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+        <v>0.63629315079088844</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>52</v>
       </c>
       <c r="B54">
-        <v>0.4820512820512821</v>
+        <v>0.48205128205128212</v>
       </c>
       <c r="C54">
         <v>1.346907993966818</v>
       </c>
       <c r="D54">
-        <v>23.22255162011754</v>
+        <v>23.222551620117539</v>
       </c>
       <c r="E54">
-        <v>0.649278725296825</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+        <v>0.64927872529682495</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -1492,506 +1633,506 @@
         <v>1.346907993966818</v>
       </c>
       <c r="D55">
-        <v>23.22255162011754</v>
+        <v>23.222551620117539</v>
       </c>
       <c r="E55">
-        <v>0.6601000373851054</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+        <v>0.66010003738510536</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>54</v>
       </c>
       <c r="B56">
-        <v>0.4997264957264957</v>
+        <v>0.49972649572649569</v>
       </c>
       <c r="C56">
-        <v>1.339031339031339</v>
+        <v>1.3390313390313391</v>
       </c>
       <c r="D56">
-        <v>23.08674722467826</v>
+        <v>23.086747224678259</v>
       </c>
       <c r="E56">
-        <v>0.6691494387220882</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
+        <v>0.66914943872208821</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>55</v>
       </c>
       <c r="B57">
-        <v>0.5077606837606838</v>
+        <v>0.50776068376068384</v>
       </c>
       <c r="C57">
-        <v>1.339031339031339</v>
+        <v>1.3390313390313391</v>
       </c>
       <c r="D57">
-        <v>23.08674722467826</v>
+        <v>23.086747224678259</v>
       </c>
       <c r="E57">
-        <v>0.6799074682835367</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
+        <v>0.67990746828353665</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>56</v>
       </c>
       <c r="B58">
-        <v>0.5157948717948717</v>
+        <v>0.51579487179487171</v>
       </c>
       <c r="C58">
-        <v>1.339031339031339</v>
+        <v>1.3390313390313391</v>
       </c>
       <c r="D58">
-        <v>23.08674722467826</v>
+        <v>23.086747224678259</v>
       </c>
       <c r="E58">
-        <v>0.6906654978449849</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
+        <v>0.69066549784498488</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>57</v>
       </c>
       <c r="B59">
-        <v>0.5254358974358974</v>
+        <v>0.52543589743589736</v>
       </c>
       <c r="C59">
         <v>1.331154684095861</v>
       </c>
       <c r="D59">
-        <v>22.95094282923898</v>
+        <v>22.950942829238979</v>
       </c>
       <c r="E59">
-        <v>0.6994364560639069</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
+        <v>0.69943645606390692</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>58</v>
       </c>
       <c r="B60">
-        <v>0.5334700854700855</v>
+        <v>0.53347008547008545</v>
       </c>
       <c r="C60">
         <v>1.331154684095861</v>
       </c>
       <c r="D60">
-        <v>22.95094282923898</v>
+        <v>22.950942829238979</v>
       </c>
       <c r="E60">
-        <v>0.7101312030985233</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
+        <v>0.71013120309852329</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>59</v>
       </c>
       <c r="B61">
-        <v>0.5415042735042735</v>
+        <v>0.54150427350427355</v>
       </c>
       <c r="C61">
-        <v>1.323278029160382</v>
+        <v>1.3232780291603821</v>
       </c>
       <c r="D61">
-        <v>22.81513843379969</v>
+        <v>22.815138433799689</v>
       </c>
       <c r="E61">
-        <v>0.7165607078246596</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
+        <v>0.71656070782465964</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>60</v>
       </c>
       <c r="B62">
-        <v>0.5495384615384615</v>
+        <v>0.54953846153846153</v>
       </c>
       <c r="C62">
-        <v>1.323278029160382</v>
+        <v>1.3232780291603821</v>
       </c>
       <c r="D62">
-        <v>22.81513843379969</v>
+        <v>22.815138433799689</v>
       </c>
       <c r="E62">
-        <v>0.7271921723324438</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+        <v>0.72719217233244382</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>61</v>
       </c>
       <c r="B63">
-        <v>0.555965811965812</v>
+        <v>0.55596581196581196</v>
       </c>
       <c r="C63">
-        <v>1.323278029160382</v>
+        <v>1.3232780291603821</v>
       </c>
       <c r="D63">
-        <v>22.81513843379969</v>
+        <v>22.815138433799689</v>
       </c>
       <c r="E63">
-        <v>0.7356973439386713</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+        <v>0.73569734393867126</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>62</v>
       </c>
       <c r="B64">
-        <v>0.5639999999999999</v>
+        <v>0.56399999999999995</v>
       </c>
       <c r="C64">
         <v>1.315401374224904</v>
       </c>
       <c r="D64">
-        <v>22.67933403836041</v>
+        <v>22.679334038360409</v>
       </c>
       <c r="E64">
-        <v>0.7418863750628455</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
+        <v>0.74188637506284549</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>63</v>
       </c>
       <c r="B65">
-        <v>0.5704273504273505</v>
+        <v>0.57042735042735049</v>
       </c>
       <c r="C65">
         <v>1.315401374224904</v>
       </c>
       <c r="D65">
-        <v>22.67933403836041</v>
+        <v>22.679334038360409</v>
       </c>
       <c r="E65">
-        <v>0.7503409206476075</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
+        <v>0.75034092064760749</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>64</v>
       </c>
       <c r="B66">
-        <v>0.5800683760683761</v>
+        <v>0.58006837606837613</v>
       </c>
       <c r="C66">
         <v>1.307524719289425</v>
       </c>
       <c r="D66">
-        <v>22.54352964292112</v>
+        <v>22.543529642921118</v>
       </c>
       <c r="E66">
-        <v>0.7584537405874762</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
+        <v>0.75845374058747617</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>65</v>
       </c>
       <c r="B67">
-        <v>0.5897094017094018</v>
+        <v>0.58970940170940178</v>
       </c>
       <c r="C67">
         <v>1.299648064353947</v>
       </c>
       <c r="D67">
-        <v>22.40772524748184</v>
+        <v>22.407725247481839</v>
       </c>
       <c r="E67">
-        <v>0.7664146824629481</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
+        <v>0.76641468246294808</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>66</v>
       </c>
       <c r="B68">
-        <v>0.5977435897435898</v>
+        <v>0.59774358974358976</v>
       </c>
       <c r="C68">
         <v>1.291771409418468</v>
       </c>
       <c r="D68">
-        <v>22.27192085204256</v>
+        <v>22.271920852042559</v>
       </c>
       <c r="E68">
-        <v>0.7721480793939317</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5">
+        <v>0.77214807939393171</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>67</v>
       </c>
       <c r="B69">
-        <v>0.6057777777777777</v>
+        <v>0.60577777777777775</v>
       </c>
       <c r="C69">
         <v>1.28389475448299</v>
       </c>
       <c r="D69">
-        <v>22.13611645660327</v>
+        <v>22.136116456603268</v>
       </c>
       <c r="E69">
-        <v>0.7777549112712511</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5">
+        <v>0.77775491127125107</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>68</v>
       </c>
       <c r="B70">
-        <v>0.6122051282051282</v>
+        <v>0.61220512820512818</v>
       </c>
       <c r="C70">
         <v>1.28389475448299</v>
       </c>
       <c r="D70">
-        <v>22.13611645660327</v>
+        <v>22.136116456603268</v>
       </c>
       <c r="E70">
-        <v>0.7860069527701503</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5">
+        <v>0.78600695277015031</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>69</v>
       </c>
       <c r="B71">
-        <v>0.6186324786324787</v>
+        <v>0.61863247863247872</v>
       </c>
       <c r="C71">
         <v>1.276018099547511</v>
       </c>
       <c r="D71">
-        <v>22.00031206116399</v>
+        <v>22.000312061163989</v>
       </c>
       <c r="E71">
-        <v>0.7893862397029818</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5">
+        <v>0.78938623970298183</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>70</v>
       </c>
       <c r="B72">
-        <v>0.625059829059829</v>
+        <v>0.62505982905982904</v>
       </c>
       <c r="C72">
-        <v>1.268141444612033</v>
+        <v>1.2681414446120329</v>
       </c>
       <c r="D72">
-        <v>21.86450766572471</v>
+        <v>21.864507665724709</v>
       </c>
       <c r="E72">
-        <v>0.7926642745928819</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5">
+        <v>0.79266427459288191</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>71</v>
       </c>
       <c r="B73">
-        <v>0.6314871794871795</v>
+        <v>0.63148717948717947</v>
       </c>
       <c r="C73">
         <v>1.260264789676554</v>
       </c>
       <c r="D73">
-        <v>21.72870327028541</v>
+        <v>21.728703270285411</v>
       </c>
       <c r="E73">
-        <v>0.7958410574398507</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5">
+        <v>0.79584105743985067</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>72</v>
       </c>
       <c r="B74">
-        <v>0.63791452991453</v>
+        <v>0.63791452991453002</v>
       </c>
       <c r="C74">
         <v>1.260264789676554</v>
       </c>
       <c r="D74">
-        <v>21.72870327028541</v>
+        <v>21.728703270285411</v>
       </c>
       <c r="E74">
-        <v>0.8039412208743532</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5">
+        <v>0.80394122087435316</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>73</v>
       </c>
       <c r="B75">
-        <v>0.6443418803418803</v>
+        <v>0.64434188034188034</v>
       </c>
       <c r="C75">
-        <v>1.252388134741076</v>
+        <v>1.2523881347410759</v>
       </c>
       <c r="D75">
-        <v>21.59289887484614</v>
+        <v>21.592898874846139</v>
       </c>
       <c r="E75">
-        <v>0.806966125656925</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5">
+        <v>0.80696612565692505</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>74</v>
       </c>
       <c r="B76">
-        <v>0.6507692307692308</v>
+        <v>0.65076923076923077</v>
       </c>
       <c r="C76">
-        <v>1.244511479805598</v>
+        <v>1.2445114798055981</v>
       </c>
       <c r="D76">
-        <v>21.45709447940686</v>
+        <v>21.457094479406859</v>
       </c>
       <c r="E76">
-        <v>0.8098897783965658</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5">
+        <v>0.80988977839656584</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>75</v>
       </c>
       <c r="B77">
-        <v>0.6555897435897435</v>
+        <v>0.65558974358974353</v>
       </c>
       <c r="C77">
-        <v>1.244511479805598</v>
+        <v>1.2445114798055981</v>
       </c>
       <c r="D77">
-        <v>21.45709447940686</v>
+        <v>21.457094479406859</v>
       </c>
       <c r="E77">
-        <v>0.8158889619402441</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5">
+        <v>0.81588896194024407</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>76</v>
       </c>
       <c r="B78">
-        <v>0.6620170940170941</v>
+        <v>0.66201709401709408</v>
       </c>
       <c r="C78">
-        <v>1.236634824870119</v>
+        <v>1.2366348248701191</v>
       </c>
       <c r="D78">
-        <v>21.32129008396756</v>
+        <v>21.321290083967561</v>
       </c>
       <c r="E78">
-        <v>0.818673393120854</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5">
+        <v>0.81867339312085396</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>77</v>
       </c>
       <c r="B79">
-        <v>0.6668376068376068</v>
+        <v>0.66683760683760684</v>
       </c>
       <c r="C79">
         <v>1.228758169934641</v>
       </c>
       <c r="D79">
-        <v>21.18548568852828</v>
+        <v>21.185485688528281</v>
       </c>
       <c r="E79">
-        <v>0.8193821574213732</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5">
+        <v>0.81938215742137321</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>78</v>
       </c>
       <c r="B80">
-        <v>0.6716581196581197</v>
+        <v>0.67165811965811972</v>
       </c>
       <c r="C80">
         <v>1.228758169934641</v>
       </c>
       <c r="D80">
-        <v>21.18548568852828</v>
+        <v>21.185485688528281</v>
       </c>
       <c r="E80">
-        <v>0.8253054019328531</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5">
+        <v>0.82530540193285307</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>79</v>
       </c>
       <c r="B81">
-        <v>0.6764786324786325</v>
+        <v>0.67647863247863249</v>
       </c>
       <c r="C81">
-        <v>1.220881514999162</v>
+        <v>1.2208815149991621</v>
       </c>
       <c r="D81">
-        <v>21.049681293089</v>
+        <v>21.049681293089002</v>
       </c>
       <c r="E81">
-        <v>0.825900257685074</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5">
+        <v>0.82590025768507402</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>80</v>
       </c>
       <c r="B82">
-        <v>0.6829059829059829</v>
+        <v>0.68290598290598292</v>
       </c>
       <c r="C82">
         <v>1.213004860063684</v>
       </c>
       <c r="D82">
-        <v>20.91387689764971</v>
+        <v>20.913876897649711</v>
       </c>
       <c r="E82">
-        <v>0.8283682762315241</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5">
+        <v>0.82836827623152409</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>81</v>
       </c>
       <c r="B83">
-        <v>0.6893333333333334</v>
+        <v>0.68933333333333335</v>
       </c>
       <c r="C83">
         <v>1.197251550192727</v>
       </c>
       <c r="D83">
-        <v>20.64226810677115</v>
+        <v>20.642268106771152</v>
       </c>
       <c r="E83">
-        <v>0.8253054019328531</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5">
+        <v>0.82530540193285307</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>82</v>
       </c>
       <c r="B84">
-        <v>0.6941538461538461</v>
+        <v>0.69415384615384612</v>
       </c>
       <c r="C84">
         <v>1.189374895257248</v>
       </c>
       <c r="D84">
-        <v>20.50646371133186</v>
+        <v>20.506463711331861</v>
       </c>
       <c r="E84">
-        <v>0.8256091580616466</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5">
+        <v>0.82560915806164659</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -2002,183 +2143,183 @@
         <v>1.18149824032177</v>
       </c>
       <c r="D85">
-        <v>20.37065931589258</v>
+        <v>20.370659315892581</v>
       </c>
       <c r="E85">
-        <v>0.8258369751582423</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5">
+        <v>0.82583697515824228</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>84</v>
       </c>
       <c r="B86">
-        <v>0.7037948717948718</v>
+        <v>0.70379487179487177</v>
       </c>
       <c r="C86">
         <v>1.173621585386291</v>
       </c>
       <c r="D86">
-        <v>20.2348549204533</v>
+        <v>20.234854920453301</v>
       </c>
       <c r="E86">
-        <v>0.825988853222639</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5">
+        <v>0.82598885322263904</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>85</v>
       </c>
       <c r="B87">
-        <v>0.7086153846153846</v>
+        <v>0.70861538461538465</v>
       </c>
       <c r="C87">
         <v>1.165744930450813</v>
       </c>
       <c r="D87">
-        <v>20.09905052501401</v>
+        <v>20.099050525014011</v>
       </c>
       <c r="E87">
-        <v>0.8260647922548375</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5">
+        <v>0.82606479225483753</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>86</v>
       </c>
       <c r="B88">
-        <v>0.7118290598290599</v>
+        <v>0.71182905982905986</v>
       </c>
       <c r="C88">
         <v>1.165744930450813</v>
       </c>
       <c r="D88">
-        <v>20.09905052501401</v>
+        <v>20.099050525014011</v>
       </c>
       <c r="E88">
-        <v>0.8298111178432948</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5">
+        <v>0.82981111784329475</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>87</v>
       </c>
       <c r="B89">
-        <v>0.715042735042735</v>
+        <v>0.71504273504273497</v>
       </c>
       <c r="C89">
-        <v>1.149991620579856</v>
+        <v>1.1499916205798559</v>
       </c>
       <c r="D89">
-        <v>19.82744173413545</v>
+        <v>19.827441734135451</v>
       </c>
       <c r="E89">
-        <v>0.8222931536556474</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5">
+        <v>0.82229315365564737</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>88</v>
       </c>
       <c r="B90">
-        <v>0.7198632478632478</v>
+        <v>0.71986324786324785</v>
       </c>
       <c r="C90">
-        <v>1.149991620579856</v>
+        <v>1.1499916205798559</v>
       </c>
       <c r="D90">
-        <v>19.82744173413545</v>
+        <v>19.827441734135451</v>
       </c>
       <c r="E90">
-        <v>0.8278367030061349</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5">
+        <v>0.82783670300613488</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>89</v>
       </c>
       <c r="B91">
-        <v>0.7246837606837606</v>
+        <v>0.72468376068376061</v>
       </c>
       <c r="C91">
         <v>1.142114965644377</v>
       </c>
       <c r="D91">
-        <v>19.69163733869616</v>
+        <v>19.691637338696161</v>
       </c>
       <c r="E91">
-        <v>0.8276721684363715</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5">
+        <v>0.82767216843637148</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>90</v>
       </c>
       <c r="B92">
-        <v>0.7278974358974359</v>
+        <v>0.72789743589743594</v>
       </c>
       <c r="C92">
-        <v>1.126361655773421</v>
+        <v>1.1263616557734211</v>
       </c>
       <c r="D92">
-        <v>19.42002854781759</v>
+        <v>19.420028547817591</v>
       </c>
       <c r="E92">
-        <v>0.8198757611306633</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5">
+        <v>0.81987576113066329</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>91</v>
       </c>
       <c r="B93">
-        <v>0.7327179487179487</v>
+        <v>0.73271794871794871</v>
       </c>
       <c r="C93">
-        <v>1.126361655773421</v>
+        <v>1.1263616557734211</v>
       </c>
       <c r="D93">
-        <v>19.42002854781759</v>
+        <v>19.420028547817591</v>
       </c>
       <c r="E93">
-        <v>0.825305401932853</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5">
+        <v>0.82530540193285296</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>92</v>
       </c>
       <c r="B94">
-        <v>0.7359316239316239</v>
+        <v>0.73593162393162392</v>
       </c>
       <c r="C94">
-        <v>1.118485000837942</v>
+        <v>1.1184850008379419</v>
       </c>
       <c r="D94">
-        <v>19.28422415237831</v>
+        <v>19.284224152378311</v>
       </c>
       <c r="E94">
-        <v>0.8231284830098303</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5">
+        <v>0.82312848300983033</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>93</v>
       </c>
       <c r="B95">
-        <v>0.7375384615384616</v>
+        <v>0.73753846153846159</v>
       </c>
       <c r="C95">
-        <v>1.110608345902463</v>
+        <v>1.1106083459024629</v>
       </c>
       <c r="D95">
         <v>19.14841975693902</v>
       </c>
       <c r="E95">
-        <v>0.8191163708086784</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5">
+        <v>0.81911637080867838</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>94</v>
       </c>
@@ -2186,55 +2327,55 @@
         <v>0.7407521367521368</v>
       </c>
       <c r="C96">
-        <v>1.110608345902463</v>
+        <v>1.1106083459024629</v>
       </c>
       <c r="D96">
         <v>19.14841975693902</v>
       </c>
       <c r="E96">
-        <v>0.822685505322006</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5">
+        <v>0.82268550532200602</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>95</v>
       </c>
       <c r="B97">
-        <v>0.7439658119658119</v>
+        <v>0.74396581196581191</v>
       </c>
       <c r="C97">
-        <v>1.102731690966985</v>
+        <v>1.1027316909669851</v>
       </c>
       <c r="D97">
-        <v>19.01261536149974</v>
+        <v>19.012615361499741</v>
       </c>
       <c r="E97">
-        <v>0.8203946778506859</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5">
+        <v>0.82039467785068587</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>96</v>
       </c>
       <c r="B98">
-        <v>0.7487863247863248</v>
+        <v>0.74878632478632479</v>
       </c>
       <c r="C98">
-        <v>1.086978381096028</v>
+        <v>1.0869783810960281</v>
       </c>
       <c r="D98">
         <v>18.74100657062117</v>
       </c>
       <c r="E98">
-        <v>0.813914547103084</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5">
+        <v>0.81391454710308397</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>97</v>
       </c>
       <c r="B99">
-        <v>0.7536068376068376</v>
+        <v>0.75360683760683755</v>
       </c>
       <c r="C99">
         <v>1.071225071225071</v>
@@ -2243,27 +2384,27 @@
         <v>18.4693977797426</v>
       </c>
       <c r="E99">
-        <v>0.8072825382910851</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5">
+        <v>0.80728253829108509</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>98</v>
       </c>
       <c r="B100">
-        <v>0.7568205128205128</v>
+        <v>0.75682051282051277</v>
       </c>
       <c r="C100">
         <v>1.055471761354114</v>
       </c>
       <c r="D100">
-        <v>18.19778898886404</v>
+        <v>18.197788988864041</v>
       </c>
       <c r="E100">
-        <v>0.7988026796955908</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5">
+        <v>0.79880267969559082</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -2277,10 +2418,10 @@
         <v>18.06198459342475</v>
       </c>
       <c r="E101">
-        <v>0.7962080960954767</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5">
+        <v>0.79620809609547671</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -2294,27 +2435,27 @@
         <v>17.92618019798547</v>
       </c>
       <c r="E102">
-        <v>0.7935628864738971</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5">
+        <v>0.79356288647389706</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>101</v>
       </c>
       <c r="B103">
-        <v>0.7680683760683761</v>
+        <v>0.76806837606837608</v>
       </c>
       <c r="C103">
-        <v>1.031841796547679</v>
+        <v>1.0318417965476789</v>
       </c>
       <c r="D103">
         <v>17.79037580254619</v>
       </c>
       <c r="E103">
-        <v>0.7925250530338515</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5">
+        <v>0.79252505303385146</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -2328,163 +2469,163 @@
         <v>17.6545714071069</v>
       </c>
       <c r="E104">
-        <v>0.7897659348639741</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5">
+        <v>0.78976593486397406</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>103</v>
       </c>
       <c r="B105">
-        <v>0.7728888888888888</v>
+        <v>0.77288888888888885</v>
       </c>
       <c r="C105">
-        <v>1.016088486676722</v>
+        <v>1.0160884866767219</v>
       </c>
       <c r="D105">
         <v>17.51876701166762</v>
       </c>
       <c r="E105">
-        <v>0.7853235014803641</v>
-      </c>
-    </row>
-    <row r="106" spans="1:5">
+        <v>0.78532350148036412</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>104</v>
       </c>
       <c r="B106">
-        <v>0.7761025641025641</v>
+        <v>0.77610256410256406</v>
       </c>
       <c r="C106">
-        <v>1.008211831741244</v>
+        <v>1.0082118317412441</v>
       </c>
       <c r="D106">
         <v>17.38296261622834</v>
       </c>
       <c r="E106">
-        <v>0.782475787772922</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5">
+        <v>0.78247578777292204</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>105</v>
       </c>
       <c r="B107">
-        <v>0.7777094017094017</v>
+        <v>0.77770940170940173</v>
       </c>
       <c r="C107">
-        <v>1.000335176805765</v>
+        <v>1.0003351768057649</v>
       </c>
       <c r="D107">
         <v>17.24715822078905</v>
       </c>
       <c r="E107">
-        <v>0.77797007186248</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5">
+        <v>0.77797007186248002</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>106</v>
       </c>
       <c r="B108">
-        <v>0.7809230769230769</v>
+        <v>0.78092307692307694</v>
       </c>
       <c r="C108">
-        <v>0.9924585218702867</v>
+        <v>0.99245852187028671</v>
       </c>
       <c r="D108">
         <v>17.11135382534977</v>
       </c>
       <c r="E108">
-        <v>0.7750337626174731</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5">
+        <v>0.77503376261747314</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>107</v>
       </c>
       <c r="B109">
-        <v>0.7825299145299145</v>
+        <v>0.78252991452991449</v>
       </c>
       <c r="C109">
-        <v>0.984581866934808</v>
+        <v>0.98458186693480798</v>
       </c>
       <c r="D109">
         <v>16.97554942991048</v>
       </c>
       <c r="E109">
-        <v>0.7704647641801989</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5">
+        <v>0.77046476418019894</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>108</v>
       </c>
       <c r="B110">
-        <v>0.7857435897435897</v>
+        <v>0.78574358974358971</v>
       </c>
       <c r="C110">
-        <v>0.984581866934808</v>
+        <v>0.98458186693480798</v>
       </c>
       <c r="D110">
         <v>16.97554942991048</v>
       </c>
       <c r="E110">
-        <v>0.7736288905218014</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5">
+        <v>0.77362889052180139</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>109</v>
       </c>
       <c r="B111">
-        <v>0.7873504273504273</v>
+        <v>0.78735042735042726</v>
       </c>
       <c r="C111">
-        <v>0.9688285570638512</v>
+        <v>0.96882855706385118</v>
       </c>
       <c r="D111">
         <v>16.70394063903192</v>
       </c>
       <c r="E111">
-        <v>0.762807578433521</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5">
+        <v>0.76280757843352098</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>110</v>
       </c>
       <c r="B112">
-        <v>0.788957264957265</v>
+        <v>0.78895726495726504</v>
       </c>
       <c r="C112">
-        <v>0.9609519021283728</v>
+        <v>0.96095190212837278</v>
       </c>
       <c r="D112">
         <v>16.56813624359263</v>
       </c>
       <c r="E112">
-        <v>0.7581499844586824</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5">
+        <v>0.75814998445868242</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>111</v>
       </c>
       <c r="B113">
-        <v>0.7905641025641026</v>
+        <v>0.79056410256410259</v>
       </c>
       <c r="C113">
-        <v>0.9609519021283728</v>
+        <v>0.96095190212837278</v>
       </c>
       <c r="D113">
         <v>16.56813624359263</v>
       </c>
       <c r="E113">
-        <v>0.7596940781133844</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5">
+        <v>0.75969407811338441</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -2492,101 +2633,101 @@
         <v>0.7937777777777778</v>
       </c>
       <c r="C114">
-        <v>0.9530752471928943</v>
+        <v>0.95307524719289427</v>
       </c>
       <c r="D114">
         <v>16.43233184815335</v>
       </c>
       <c r="E114">
-        <v>0.7565299517717818</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5">
+        <v>0.75652995177178184</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>113</v>
       </c>
       <c r="B115">
-        <v>0.7953846153846154</v>
+        <v>0.79538461538461536</v>
       </c>
       <c r="C115">
-        <v>0.9451985922574158</v>
+        <v>0.94519859225741576</v>
       </c>
       <c r="D115">
-        <v>16.29652745271406</v>
+        <v>16.296527452714059</v>
       </c>
       <c r="E115">
-        <v>0.7517964187647445</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
+        <v>0.75179641876474446</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>114</v>
       </c>
       <c r="B116">
-        <v>0.7985982905982907</v>
+        <v>0.79859829059829068</v>
       </c>
       <c r="C116">
-        <v>0.9373219373219374</v>
+        <v>0.93732193732193736</v>
       </c>
       <c r="D116">
         <v>16.16072305727478</v>
       </c>
       <c r="E116">
-        <v>0.7485436968855773</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
+        <v>0.74854369688557731</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>115</v>
       </c>
       <c r="B117">
-        <v>0.8002051282051282</v>
+        <v>0.80020512820512824</v>
       </c>
       <c r="C117">
-        <v>0.9294452823864588</v>
+        <v>0.92944528238645885</v>
       </c>
       <c r="D117">
         <v>16.0249186618355</v>
       </c>
       <c r="E117">
-        <v>0.743746881351708</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5">
+        <v>0.74374688135170797</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>116</v>
       </c>
       <c r="B118">
-        <v>0.8018119658119658</v>
+        <v>0.80181196581196579</v>
       </c>
       <c r="C118">
-        <v>0.9215686274509803</v>
+        <v>0.92156862745098034</v>
       </c>
       <c r="D118">
-        <v>15.88911426639621</v>
+        <v>15.889114266396209</v>
       </c>
       <c r="E118">
-        <v>0.7389247528071057</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5">
+        <v>0.73892475280710568</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>117</v>
       </c>
       <c r="B119">
-        <v>0.8034188034188035</v>
+        <v>0.80341880341880345</v>
       </c>
       <c r="C119">
-        <v>0.9136919725155019</v>
+        <v>0.91369197251550194</v>
       </c>
       <c r="D119">
-        <v>15.75330987095693</v>
+        <v>15.753309870956929</v>
       </c>
       <c r="E119">
-        <v>0.7340773112517708</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5">
+        <v>0.73407731125177078</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -2594,101 +2735,101 @@
         <v>0.805025641025641</v>
       </c>
       <c r="C120">
-        <v>0.9058153175800235</v>
+        <v>0.90581531758002354</v>
       </c>
       <c r="D120">
         <v>15.61750547551765</v>
       </c>
       <c r="E120">
-        <v>0.7292045566857031</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
+        <v>0.72920455668570305</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>119</v>
       </c>
       <c r="B121">
-        <v>0.8066324786324786</v>
+        <v>0.80663247863247856</v>
       </c>
       <c r="C121">
-        <v>0.9058153175800235</v>
+        <v>0.90581531758002354</v>
       </c>
       <c r="D121">
         <v>15.61750547551765</v>
       </c>
       <c r="E121">
-        <v>0.7306600548028401</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5">
+        <v>0.73066005480284013</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>120</v>
       </c>
       <c r="B122">
-        <v>0.8082393162393163</v>
+        <v>0.80823931623931633</v>
       </c>
       <c r="C122">
-        <v>0.8979386626445449</v>
+        <v>0.89793866264454492</v>
       </c>
       <c r="D122">
-        <v>15.48170108007836</v>
+        <v>15.481701080078359</v>
       </c>
       <c r="E122">
-        <v>0.7257493307206732</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5">
+        <v>0.72574933072067316</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>121</v>
       </c>
       <c r="B123">
-        <v>0.8098461538461539</v>
+        <v>0.80984615384615388</v>
       </c>
       <c r="C123">
-        <v>0.8979386626445449</v>
+        <v>0.89793866264454492</v>
       </c>
       <c r="D123">
-        <v>15.48170108007836</v>
+        <v>15.481701080078359</v>
       </c>
       <c r="E123">
-        <v>0.7271921723324438</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5">
+        <v>0.72719217233244382</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>122</v>
       </c>
       <c r="B124">
-        <v>0.8114529914529914</v>
+        <v>0.81145299145299143</v>
       </c>
       <c r="C124">
-        <v>0.8900620077090664</v>
+        <v>0.89006200770906641</v>
       </c>
       <c r="D124">
-        <v>15.34589668463908</v>
+        <v>15.345896684639079</v>
       </c>
       <c r="E124">
-        <v>0.7222434787341775</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5">
+        <v>0.72224347873417749</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>123</v>
       </c>
       <c r="B125">
-        <v>0.8114529914529914</v>
+        <v>0.81145299145299143</v>
       </c>
       <c r="C125">
-        <v>0.882185352773588</v>
+        <v>0.88218535277358801</v>
       </c>
       <c r="D125">
-        <v>15.21009228919979</v>
+        <v>15.210092289199791</v>
       </c>
       <c r="E125">
         <v>0.7158519435241405</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>124</v>
       </c>
@@ -2696,33 +2837,33 @@
         <v>0.8130598290598291</v>
       </c>
       <c r="C126">
-        <v>0.882185352773588</v>
+        <v>0.88218535277358801</v>
       </c>
       <c r="D126">
-        <v>15.21009228919979</v>
+        <v>15.210092289199791</v>
       </c>
       <c r="E126">
-        <v>0.7172694721251784</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5">
+        <v>0.71726947212517844</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>125</v>
       </c>
       <c r="B127">
-        <v>0.8146666666666667</v>
+        <v>0.81466666666666665</v>
       </c>
       <c r="C127">
-        <v>0.8743086978381095</v>
+        <v>0.87430869783810949</v>
       </c>
       <c r="D127">
-        <v>15.07428789376051</v>
+        <v>15.074287893760509</v>
       </c>
       <c r="E127">
-        <v>0.7122701525054466</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5">
+        <v>0.71227015250544656</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -2730,16 +2871,16 @@
         <v>0.8162735042735042</v>
       </c>
       <c r="C128">
-        <v>0.8743086978381095</v>
+        <v>0.87430869783810949</v>
       </c>
       <c r="D128">
-        <v>15.07428789376051</v>
+        <v>15.074287893760509</v>
       </c>
       <c r="E128">
-        <v>0.713675024601118</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5">
+        <v>0.71367502460111798</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -2747,21 +2888,21 @@
         <v>0.8162735042735042</v>
       </c>
       <c r="C129">
-        <v>0.8664320429026311</v>
+        <v>0.86643204290263109</v>
       </c>
       <c r="D129">
-        <v>14.93848349832123</v>
+        <v>14.938483498321229</v>
       </c>
       <c r="E129">
-        <v>0.7072455198749819</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5">
+        <v>0.70724551987498185</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>128</v>
       </c>
       <c r="B130">
-        <v>0.8339487179487179</v>
+        <v>0.83394871794871794</v>
       </c>
       <c r="C130">
         <v>0.7246522540640189</v>
@@ -2770,44 +2911,44 @@
         <v>12.49400438041412</v>
       </c>
       <c r="E130">
-        <v>0.6043228182353372</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5">
+        <v>0.60432281823533718</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>129</v>
       </c>
       <c r="B131">
-        <v>0.8516239316239317</v>
+        <v>0.85162393162393168</v>
       </c>
       <c r="C131">
         <v>0.6143790849673203</v>
       </c>
       <c r="D131">
-        <v>10.59274284426414</v>
+        <v>10.592742844264141</v>
       </c>
       <c r="E131">
-        <v>0.5232199318473829</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5">
+        <v>0.52321993184738291</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>130</v>
       </c>
       <c r="B132">
-        <v>0.8644786324786324</v>
+        <v>0.86447863247863244</v>
       </c>
       <c r="C132">
-        <v>0.5119825708061002</v>
+        <v>0.51198257080610021</v>
       </c>
       <c r="D132">
-        <v>8.827285703553452</v>
+        <v>8.8272857035534518</v>
       </c>
       <c r="E132">
-        <v>0.4425979926633521</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5">
+        <v>0.44259799266335209</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -2815,157 +2956,157 @@
         <v>0.8773333333333333</v>
       </c>
       <c r="C133">
-        <v>0.4332160214513155</v>
+        <v>0.43321602145131549</v>
       </c>
       <c r="D133">
-        <v>7.469241749160613</v>
+        <v>7.4692417491606129</v>
       </c>
       <c r="E133">
-        <v>0.3800748561532875</v>
-      </c>
-    </row>
-    <row r="134" spans="1:5">
+        <v>0.38007485615328751</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>132</v>
       </c>
       <c r="B134">
-        <v>0.8869743589743589</v>
+        <v>0.88697435897435895</v>
       </c>
       <c r="C134">
-        <v>0.3702027819674878</v>
+        <v>0.37020278196748779</v>
       </c>
       <c r="D134">
-        <v>6.382806585646342</v>
+        <v>6.3828065856463416</v>
       </c>
       <c r="E134">
-        <v>0.3283603752261369</v>
-      </c>
-    </row>
-    <row r="135" spans="1:5">
+        <v>0.32836037522613692</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>133</v>
       </c>
       <c r="B135">
-        <v>0.8966153846153846</v>
+        <v>0.89661538461538459</v>
       </c>
       <c r="C135">
-        <v>0.3150661974191385</v>
+        <v>0.31506619741913849</v>
       </c>
       <c r="D135">
-        <v>5.432175817571354</v>
+        <v>5.4321758175713537</v>
       </c>
       <c r="E135">
-        <v>0.2824931997782676</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5">
+        <v>0.28249319977826759</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>134</v>
       </c>
       <c r="B136">
-        <v>0.903042735042735</v>
+        <v>0.90304273504273502</v>
       </c>
       <c r="C136">
-        <v>0.2678062678062678</v>
+        <v>0.26780626780626782</v>
       </c>
       <c r="D136">
-        <v>4.617349444935651</v>
+        <v>4.6173494449356509</v>
       </c>
       <c r="E136">
-        <v>0.2418405045413592</v>
-      </c>
-    </row>
-    <row r="137" spans="1:5">
+        <v>0.24184050454135919</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>135</v>
       </c>
       <c r="B137">
-        <v>0.9094700854700856</v>
+        <v>0.90947008547008557</v>
       </c>
       <c r="C137">
         <v>0.220546338193397</v>
       </c>
       <c r="D137">
-        <v>3.802523072299948</v>
+        <v>3.8025230722999481</v>
       </c>
       <c r="E137">
         <v>0.2005802970468632</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>136</v>
       </c>
       <c r="B138">
-        <v>0.9142905982905983</v>
+        <v>0.91429059829059833</v>
       </c>
       <c r="C138">
-        <v>0.1890397184514832</v>
+        <v>0.18903971845148321</v>
       </c>
       <c r="D138">
-        <v>3.259305490542813</v>
+        <v>3.2593054905428129</v>
       </c>
       <c r="E138">
         <v>0.1728372372836928</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>137</v>
       </c>
       <c r="B139">
-        <v>0.9207179487179488</v>
+        <v>0.92071794871794876</v>
       </c>
       <c r="C139">
-        <v>0.1654097536450478</v>
+        <v>0.16540975364504781</v>
       </c>
       <c r="D139">
-        <v>2.851892304224961</v>
+        <v>2.8518923042249611</v>
       </c>
       <c r="E139">
-        <v>0.1522957290740096</v>
-      </c>
-    </row>
-    <row r="140" spans="1:5">
+        <v>0.15229572907400959</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>138</v>
       </c>
       <c r="B140">
-        <v>0.923931623931624</v>
+        <v>0.92393162393162398</v>
       </c>
       <c r="C140">
-        <v>0.1417797888386124</v>
+        <v>0.14177978883861239</v>
       </c>
       <c r="D140">
-        <v>2.44447911790711</v>
+        <v>2.4444791179071101</v>
       </c>
       <c r="E140">
-        <v>0.1309948305423418</v>
-      </c>
-    </row>
-    <row r="141" spans="1:5">
+        <v>0.13099483054234179</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>139</v>
       </c>
       <c r="B141">
-        <v>0.9287521367521369</v>
+        <v>0.92875213675213686</v>
       </c>
       <c r="C141">
         <v>0.118149824032177</v>
       </c>
       <c r="D141">
-        <v>2.037065931589258</v>
+        <v>2.0370659315892579</v>
       </c>
       <c r="E141">
         <v>0.1097319015267733</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>140</v>
       </c>
       <c r="B142">
-        <v>0.931965811965812</v>
+        <v>0.93196581196581196</v>
       </c>
       <c r="C142">
         <v>0.1023965141612201</v>
@@ -2974,180 +3115,180 @@
         <v>1.76545714071069</v>
       </c>
       <c r="E142">
-        <v>0.09543005046273022</v>
-      </c>
-    </row>
-    <row r="143" spans="1:5">
+        <v>9.5430050462730218E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>141</v>
       </c>
       <c r="B143">
-        <v>0.9335726495726496</v>
+        <v>0.93357264957264963</v>
       </c>
       <c r="C143">
-        <v>0.08664320429026312</v>
+        <v>8.6643204290263121E-2</v>
       </c>
       <c r="D143">
-        <v>1.493848349832123</v>
+        <v>1.4938483498321229</v>
       </c>
       <c r="E143">
-        <v>0.0808877257967253</v>
-      </c>
-    </row>
-    <row r="144" spans="1:5">
+        <v>8.0887725796725304E-2</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>142</v>
       </c>
       <c r="B144">
-        <v>0.9367863247863247</v>
+        <v>0.93678632478632473</v>
       </c>
       <c r="C144">
-        <v>0.07876654935478464</v>
+        <v>7.8766549354784637E-2</v>
       </c>
       <c r="D144">
         <v>1.358043954392838</v>
       </c>
       <c r="E144">
-        <v>0.07378742628616936</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5">
+        <v>7.3787426286169355E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>143</v>
       </c>
       <c r="B145">
-        <v>0.9383931623931625</v>
+        <v>0.93839316239316251</v>
       </c>
       <c r="C145">
-        <v>0.06301323948382773</v>
+        <v>6.3013239483827727E-2</v>
       </c>
       <c r="D145">
-        <v>1.086435163514271</v>
+        <v>1.0864351635142711</v>
       </c>
       <c r="E145">
-        <v>0.05913119307186679</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5">
+        <v>5.9131193071866789E-2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>144</v>
       </c>
       <c r="B146">
-        <v>0.9400000000000001</v>
+        <v>0.94000000000000006</v>
       </c>
       <c r="C146">
-        <v>0.05513658454834925</v>
+        <v>5.513658454834925E-2</v>
       </c>
       <c r="D146">
-        <v>0.950630768074987</v>
+        <v>0.95063076807498703</v>
       </c>
       <c r="E146">
-        <v>0.0518283894754483</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
+        <v>5.1828389475448301E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>145</v>
       </c>
       <c r="B147">
-        <v>0.9432136752136753</v>
+        <v>0.94321367521367527</v>
       </c>
       <c r="C147">
-        <v>0.04725992961287079</v>
+        <v>4.7259929612870788E-2</v>
       </c>
       <c r="D147">
-        <v>0.8148263726357032</v>
+        <v>0.81482637263570323</v>
       </c>
       <c r="E147">
-        <v>0.04457621190049546</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
+        <v>4.457621190049546E-2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>146</v>
       </c>
       <c r="B148">
-        <v>0.9448205128205128</v>
+        <v>0.94482051282051283</v>
       </c>
       <c r="C148">
-        <v>0.03938327467739232</v>
+        <v>3.9383274677392319E-2</v>
       </c>
       <c r="D148">
-        <v>0.6790219771964192</v>
+        <v>0.67902197719641921</v>
       </c>
       <c r="E148">
-        <v>0.03721012577724492</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
+        <v>3.7210125777244918E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>147</v>
       </c>
       <c r="B149">
-        <v>0.9464273504273504</v>
+        <v>0.94642735042735038</v>
       </c>
       <c r="C149">
-        <v>0.03150661974191386</v>
+        <v>3.1506619741913863E-2</v>
       </c>
       <c r="D149">
-        <v>0.5432175817571355</v>
+        <v>0.54321758175713553</v>
       </c>
       <c r="E149">
-        <v>0.02981872664326159</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
+        <v>2.981872664326159E-2</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>148</v>
       </c>
       <c r="B150">
-        <v>0.9464273504273504</v>
+        <v>0.94642735042735038</v>
       </c>
       <c r="C150">
-        <v>0.03150661974191386</v>
+        <v>3.1506619741913863E-2</v>
       </c>
       <c r="D150">
-        <v>0.5432175817571355</v>
+        <v>0.54321758175713553</v>
       </c>
       <c r="E150">
-        <v>0.02981872664326159</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
+        <v>2.981872664326159E-2</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>149</v>
       </c>
       <c r="B151">
-        <v>0.948034188034188</v>
+        <v>0.94803418803418804</v>
       </c>
       <c r="C151">
-        <v>0.02362996480643539</v>
+        <v>2.3629964806435391E-2</v>
       </c>
       <c r="D151">
-        <v>0.4074131863178516</v>
+        <v>0.40741318631785162</v>
       </c>
       <c r="E151">
-        <v>0.02240201449854542</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
+        <v>2.2402014498545422E-2</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>150</v>
       </c>
       <c r="B152">
-        <v>0.948034188034188</v>
+        <v>0.94803418803418804</v>
       </c>
       <c r="C152">
-        <v>0.02362996480643539</v>
+        <v>2.3629964806435391E-2</v>
       </c>
       <c r="D152">
-        <v>0.4074131863178516</v>
+        <v>0.40741318631785162</v>
       </c>
       <c r="E152">
-        <v>0.02240201449854542</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
+        <v>2.2402014498545422E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>151</v>
       </c>
@@ -3155,16 +3296,16 @@
         <v>0.9496410256410257</v>
       </c>
       <c r="C153">
-        <v>0.02362996480643539</v>
+        <v>2.3629964806435391E-2</v>
       </c>
       <c r="D153">
-        <v>0.4074131863178516</v>
+        <v>0.40741318631785162</v>
       </c>
       <c r="E153">
-        <v>0.02243998401464465</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
+        <v>2.243998401464465E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>152</v>
       </c>
@@ -3172,242 +3313,242 @@
         <v>0.9496410256410257</v>
       </c>
       <c r="C154">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D154">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E154">
-        <v>0.01495998934309643</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
+        <v>1.495998934309643E-2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>153</v>
       </c>
       <c r="B155">
-        <v>0.9512478632478633</v>
+        <v>0.95124786324786326</v>
       </c>
       <c r="C155">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D155">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E155">
-        <v>0.01498530235382925</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
+        <v>1.498530235382925E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>154</v>
       </c>
       <c r="B156">
-        <v>0.9528547008547009</v>
+        <v>0.95285470085470092</v>
       </c>
       <c r="C156">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D156">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E156">
-        <v>0.01501061536456207</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
+        <v>1.5010615364562069E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>155</v>
       </c>
       <c r="B157">
-        <v>0.9528547008547009</v>
+        <v>0.95285470085470092</v>
       </c>
       <c r="C157">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D157">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E157">
-        <v>0.01501061536456207</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
+        <v>1.5010615364562069E-2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>156</v>
       </c>
       <c r="B158">
-        <v>0.9528547008547009</v>
+        <v>0.95285470085470092</v>
       </c>
       <c r="C158">
-        <v>0.01575330987095693</v>
+        <v>1.5753309870956932E-2</v>
       </c>
       <c r="D158">
-        <v>0.2716087908785678</v>
+        <v>0.27160879087856782</v>
       </c>
       <c r="E158">
-        <v>0.01501061536456207</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
+        <v>1.5010615364562069E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>157</v>
       </c>
       <c r="B159">
-        <v>0.9528547008547009</v>
+        <v>0.95285470085470092</v>
       </c>
       <c r="C159">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D159">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E159">
-        <v>0.007505307682281037</v>
-      </c>
-    </row>
-    <row r="160" spans="1:5">
+        <v>7.5053076822810373E-3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>158</v>
       </c>
       <c r="B160">
-        <v>0.9544615384615385</v>
+        <v>0.95446153846153847</v>
       </c>
       <c r="C160">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D160">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E160">
-        <v>0.007517964187647446</v>
-      </c>
-    </row>
-    <row r="161" spans="1:5">
+        <v>7.5179641876474456E-3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>159</v>
       </c>
       <c r="B161">
-        <v>0.9544615384615385</v>
+        <v>0.95446153846153847</v>
       </c>
       <c r="C161">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D161">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E161">
-        <v>0.007517964187647446</v>
-      </c>
-    </row>
-    <row r="162" spans="1:5">
+        <v>7.5179641876474456E-3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>160</v>
       </c>
       <c r="B162">
-        <v>0.9544615384615385</v>
+        <v>0.95446153846153847</v>
       </c>
       <c r="C162">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D162">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E162">
-        <v>0.007517964187647446</v>
-      </c>
-    </row>
-    <row r="163" spans="1:5">
+        <v>7.5179641876474456E-3</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>161</v>
       </c>
       <c r="B163">
-        <v>0.9544615384615385</v>
+        <v>0.95446153846153847</v>
       </c>
       <c r="C163">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D163">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E163">
-        <v>0.007517964187647446</v>
-      </c>
-    </row>
-    <row r="164" spans="1:5">
+        <v>7.5179641876474456E-3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>162</v>
       </c>
       <c r="B164">
-        <v>0.9544615384615385</v>
+        <v>0.95446153846153847</v>
       </c>
       <c r="C164">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D164">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E164">
-        <v>0.007517964187647446</v>
-      </c>
-    </row>
-    <row r="165" spans="1:5">
+        <v>7.5179641876474456E-3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>163</v>
       </c>
       <c r="B165">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C165">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D165">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E165">
-        <v>0.007530620693013856</v>
-      </c>
-    </row>
-    <row r="166" spans="1:5">
+        <v>7.5306206930138564E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>164</v>
       </c>
       <c r="B166">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C166">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D166">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E166">
-        <v>0.007530620693013856</v>
-      </c>
-    </row>
-    <row r="167" spans="1:5">
+        <v>7.5306206930138564E-3</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>165</v>
       </c>
       <c r="B167">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C167">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D167">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E167">
-        <v>0.007530620693013856</v>
-      </c>
-    </row>
-    <row r="168" spans="1:5">
+        <v>7.5306206930138564E-3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>166</v>
       </c>
       <c r="B168">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3419,29 +3560,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>167</v>
       </c>
       <c r="B169">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C169">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D169">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E169">
-        <v>0.007530620693013856</v>
-      </c>
-    </row>
-    <row r="170" spans="1:5">
+        <v>7.5306206930138564E-3</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>168</v>
       </c>
       <c r="B170">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C170">
         <v>0</v>
@@ -3453,12 +3594,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>169</v>
       </c>
       <c r="B171">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -3470,29 +3611,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>170</v>
       </c>
       <c r="B172">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C172">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D172">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E172">
-        <v>0.007530620693013856</v>
-      </c>
-    </row>
-    <row r="173" spans="1:5">
+        <v>7.5306206930138564E-3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>171</v>
       </c>
       <c r="B173">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3504,12 +3645,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>172</v>
       </c>
       <c r="B174">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3521,12 +3662,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>173</v>
       </c>
       <c r="B175">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3538,12 +3679,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>174</v>
       </c>
       <c r="B176">
-        <v>0.956068376068376</v>
+        <v>0.95606837606837602</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -3555,12 +3696,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>175</v>
       </c>
       <c r="B177">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C177">
         <v>0</v>
@@ -3572,12 +3713,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>176</v>
       </c>
       <c r="B178">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3589,12 +3730,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>177</v>
       </c>
       <c r="B179">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C179">
         <v>0</v>
@@ -3606,12 +3747,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>178</v>
       </c>
       <c r="B180">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C180">
         <v>0</v>
@@ -3623,12 +3764,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>179</v>
       </c>
       <c r="B181">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -3640,29 +3781,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>180</v>
       </c>
       <c r="B182">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C182">
-        <v>0.007876654935478466</v>
+        <v>7.8766549354784658E-3</v>
       </c>
       <c r="D182">
-        <v>0.1358043954392839</v>
+        <v>0.13580439543928391</v>
       </c>
       <c r="E182">
-        <v>0.007543277198380266</v>
-      </c>
-    </row>
-    <row r="183" spans="1:5">
+        <v>7.5432771983802663E-3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>181</v>
       </c>
       <c r="B183">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -3674,12 +3815,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>182</v>
       </c>
       <c r="B184">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -3691,12 +3832,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>183</v>
       </c>
       <c r="B185">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -3708,12 +3849,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>184</v>
       </c>
       <c r="B186">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -3725,12 +3866,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>185</v>
       </c>
       <c r="B187">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -3742,12 +3883,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>186</v>
       </c>
       <c r="B188">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -3759,12 +3900,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>187</v>
       </c>
       <c r="B189">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -3776,12 +3917,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>188</v>
       </c>
       <c r="B190">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -3793,12 +3934,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>189</v>
       </c>
       <c r="B191">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -3810,12 +3951,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>190</v>
       </c>
       <c r="B192">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C192">
         <v>0</v>
@@ -3827,12 +3968,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>191</v>
       </c>
       <c r="B193">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -3844,12 +3985,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>192</v>
       </c>
       <c r="B194">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C194">
         <v>0</v>
@@ -3861,12 +4002,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>193</v>
       </c>
       <c r="B195">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C195">
         <v>0</v>
@@ -3878,12 +4019,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>194</v>
       </c>
       <c r="B196">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -3895,12 +4036,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>195</v>
       </c>
       <c r="B197">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -3912,12 +4053,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>196</v>
       </c>
       <c r="B198">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -3929,12 +4070,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>197</v>
       </c>
       <c r="B199">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -3946,12 +4087,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>198</v>
       </c>
       <c r="B200">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -3963,12 +4104,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>199</v>
       </c>
       <c r="B201">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -3980,12 +4121,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>200</v>
       </c>
       <c r="B202">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -3997,12 +4138,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>201</v>
       </c>
       <c r="B203">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -4014,12 +4155,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>202</v>
       </c>
       <c r="B204">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -4031,12 +4172,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>203</v>
       </c>
       <c r="B205">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -4048,12 +4189,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>204</v>
       </c>
       <c r="B206">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -4065,12 +4206,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>205</v>
       </c>
       <c r="B207">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -4082,12 +4223,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>206</v>
       </c>
       <c r="B208">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C208">
         <v>0</v>
@@ -4099,12 +4240,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>207</v>
       </c>
       <c r="B209">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -4116,12 +4257,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>208</v>
       </c>
       <c r="B210">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -4133,12 +4274,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>209</v>
       </c>
       <c r="B211">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -4150,12 +4291,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>210</v>
       </c>
       <c r="B212">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -4167,12 +4308,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>211</v>
       </c>
       <c r="B213">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -4184,12 +4325,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>212</v>
       </c>
       <c r="B214">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -4201,12 +4342,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>213</v>
       </c>
       <c r="B215">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -4218,12 +4359,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>214</v>
       </c>
       <c r="B216">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -4235,12 +4376,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>215</v>
       </c>
       <c r="B217">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -4252,12 +4393,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>216</v>
       </c>
       <c r="B218">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C218">
         <v>0</v>
@@ -4269,12 +4410,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>217</v>
       </c>
       <c r="B219">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C219">
         <v>0</v>
@@ -4286,12 +4427,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>218</v>
       </c>
       <c r="B220">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -4303,12 +4444,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>219</v>
       </c>
       <c r="B221">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -4320,12 +4461,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>220</v>
       </c>
       <c r="B222">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C222">
         <v>0</v>
@@ -4337,12 +4478,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>221</v>
       </c>
       <c r="B223">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -4354,12 +4495,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>222</v>
       </c>
       <c r="B224">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C224">
         <v>0</v>
@@ -4371,12 +4512,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>223</v>
       </c>
       <c r="B225">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -4388,12 +4529,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>224</v>
       </c>
       <c r="B226">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -4405,12 +4546,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>225</v>
       </c>
       <c r="B227">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -4422,12 +4563,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>226</v>
       </c>
       <c r="B228">
-        <v>0.9576752136752137</v>
+        <v>0.95767521367521369</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -4439,12 +4580,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>227</v>
       </c>
       <c r="B229">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -4456,12 +4597,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>228</v>
       </c>
       <c r="B230">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -4473,12 +4614,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>229</v>
       </c>
       <c r="B231">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -4490,12 +4631,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>230</v>
       </c>
       <c r="B232">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -4507,12 +4648,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>231</v>
       </c>
       <c r="B233">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -4524,12 +4665,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>232</v>
       </c>
       <c r="B234">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C234">
         <v>0</v>
@@ -4541,12 +4682,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>233</v>
       </c>
       <c r="B235">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -4558,12 +4699,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>234</v>
       </c>
       <c r="B236">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -4575,12 +4716,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>235</v>
       </c>
       <c r="B237">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -4592,12 +4733,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>236</v>
       </c>
       <c r="B238">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -4609,12 +4750,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>237</v>
       </c>
       <c r="B239">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -4626,12 +4767,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>238</v>
       </c>
       <c r="B240">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -4643,12 +4784,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>239</v>
       </c>
       <c r="B241">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -4660,12 +4801,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>240</v>
       </c>
       <c r="B242">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -4677,12 +4818,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>241</v>
       </c>
       <c r="B243">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -4694,12 +4835,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>242</v>
       </c>
       <c r="B244">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C244">
         <v>0</v>
@@ -4711,12 +4852,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>243</v>
       </c>
       <c r="B245">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C245">
         <v>0</v>
@@ -4728,12 +4869,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>244</v>
       </c>
       <c r="B246">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -4745,12 +4886,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>245</v>
       </c>
       <c r="B247">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C247">
         <v>0</v>
@@ -4762,12 +4903,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>246</v>
       </c>
       <c r="B248">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C248">
         <v>0</v>
@@ -4779,12 +4920,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>247</v>
       </c>
       <c r="B249">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -4796,12 +4937,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>248</v>
       </c>
       <c r="B250">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -4813,12 +4954,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>249</v>
       </c>
       <c r="B251">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -4830,12 +4971,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>250</v>
       </c>
       <c r="B252">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -4847,12 +4988,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>251</v>
       </c>
       <c r="B253">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -4864,12 +5005,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>252</v>
       </c>
       <c r="B254">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -4881,12 +5022,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>253</v>
       </c>
       <c r="B255">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -4898,7 +5039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>254</v>
       </c>
@@ -4915,12 +5056,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>255</v>
       </c>
       <c r="B257">
-        <v>0.9592820512820514</v>
+        <v>0.95928205128205135</v>
       </c>
       <c r="C257">
         <v>0</v>
